--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9503364E-E617-4CF8-B828-4EC6A116D0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177BCFCA-631C-44C8-B3E6-77478DE56CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
+    <sheet name="T2" sheetId="2" r:id="rId2"/>
+    <sheet name="T3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>A</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
   <si>
     <t>B</t>
   </si>
@@ -48,6 +47,9 @@
   </si>
   <si>
     <t>Reduction</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -386,7 +388,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>-0.22</v>
@@ -394,11 +396,97 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <f>B3*(B1-B2)/B2</f>
         <v>-0.16681318681318683</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B3*(B1-B2)/B2</f>
+        <v>-0.17137931034482759</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>(B2*B1)/-B3</f>
+        <v>-0.21777777777777779</v>
       </c>
     </row>
   </sheetData>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177BCFCA-631C-44C8-B3E6-77478DE56CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDF4679-B3B3-4200-8643-A758A0FE23BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
     <sheet name="T2" sheetId="2" r:id="rId2"/>
     <sheet name="T3" sheetId="3" r:id="rId3"/>
+    <sheet name="T4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="4">
   <si>
     <t>B</t>
   </si>
@@ -461,7 +462,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -477,7 +478,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>90</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -485,8 +486,43 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <f>(B2*B1)/-B3</f>
+        <f>-(B2*B1)/B3</f>
         <v>-0.21777777777777779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>B2*B1</f>
+        <v>-5.7200000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDF4679-B3B3-4200-8643-A758A0FE23BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760DE46B-1A41-4CB7-AC98-FEEFDD21227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
     <sheet name="T2" sheetId="2" r:id="rId2"/>
     <sheet name="T3" sheetId="3" r:id="rId3"/>
     <sheet name="T4" sheetId="4" r:id="rId4"/>
+    <sheet name="T55" sheetId="5" r:id="rId5"/>
+    <sheet name="T5" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="4">
   <si>
     <t>B</t>
   </si>
@@ -528,4 +530,83 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5ED6D57-DE29-4DAC-A3AA-80DD11128A92}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>(B2-B1)/B2*B3</f>
+        <v>-0.13200000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEBE0D8-DEE9-4520-B548-EAFE23AFA71B}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>B1*B2</f>
+        <v>-3.5200000000000002E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760DE46B-1A41-4CB7-AC98-FEEFDD21227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B86DC95-EB8D-4FC3-B7BC-412313083EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <sheet name="T4" sheetId="4" r:id="rId4"/>
     <sheet name="T55" sheetId="5" r:id="rId5"/>
     <sheet name="T5" sheetId="6" r:id="rId6"/>
+    <sheet name="T6" sheetId="7" r:id="rId7"/>
+    <sheet name="T7" sheetId="8" r:id="rId8"/>
+    <sheet name="T8" sheetId="9" r:id="rId9"/>
+    <sheet name="T9" sheetId="10" r:id="rId10"/>
+    <sheet name="T11" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="9">
   <si>
     <t>B</t>
   </si>
@@ -53,6 +58,21 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
   </si>
 </sst>
 </file>
@@ -88,8 +108,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,6 +432,158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B16458-C940-4002-A635-0E8C338DCCC2}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <f>(B2/B1)*B3*B4*B5*B6*B7*B8</f>
+        <v>-2.6144000000000004E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8198844C-4C52-40D3-A5CC-C3F133397CB1}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>307.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>763.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>((1-B1)*B2*B5+B1*(B3/B4)*B6)/((1-B1)*B2*B5+B1*B3*B5) -1</f>
+        <v>-3.3192034620550204E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
   <dimension ref="A1:B4"/>
@@ -609,4 +782,128 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D512145F-AAB1-4862-93C2-E8C630C31BD4}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B1*B2*B3</f>
+        <v>-0.221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE34028-78B5-4730-BB77-EDE25BEED080}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B1*B2*B3</f>
+        <v>-2.7999999999999997E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6836B869-383D-4226-9FF3-A319F5FB364A}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <f>0.08</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>B1*B2</f>
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B86DC95-EB8D-4FC3-B7BC-412313083EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D23FFC4-3C98-400F-B2B8-25E7478122A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19050" yWindow="9780" windowWidth="15915" windowHeight="10080" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="T8" sheetId="9" r:id="rId9"/>
     <sheet name="T9" sheetId="10" r:id="rId10"/>
     <sheet name="T11" sheetId="11" r:id="rId11"/>
+    <sheet name="T12" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="9">
   <si>
     <t>B</t>
   </si>
@@ -584,6 +585,65 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD0EB77-86F6-45D0-A287-CA923C8E64E0}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>((B1-B2)/B2)*B3*B4*B5</f>
+        <v>-8.0000000000000016E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D23FFC4-3C98-400F-B2B8-25E7478122A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5936755-045A-4AB6-B398-19808B24EECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19050" yWindow="9780" windowWidth="15915" windowHeight="10080" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="T9" sheetId="10" r:id="rId10"/>
     <sheet name="T11" sheetId="11" r:id="rId11"/>
     <sheet name="T12" sheetId="12" r:id="rId12"/>
+    <sheet name="T13" sheetId="13" r:id="rId13"/>
+    <sheet name="T14" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -74,6 +76,15 @@
   </si>
   <si>
     <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -644,6 +655,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB85472-F537-4DE8-92F9-12CB7CBA9F10}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>B1*B2</f>
+        <v>0.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A9B71FA-36E9-4AA9-A810-0D608806979B}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>205.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0.32700000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>307.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <f>(B1*B3*(B5-B4)*(B6-(B7*B8*B10*B11)))/(-B2*B9)</f>
+        <v>-5.447830172357724E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5936755-045A-4AB6-B398-19808B24EECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C651359A-5A84-4809-89FE-BC8B21F6289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="T12" sheetId="12" r:id="rId12"/>
     <sheet name="T13" sheetId="13" r:id="rId13"/>
     <sheet name="T14" sheetId="14" r:id="rId14"/>
+    <sheet name="T15" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -798,6 +799,66 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE7A069-D1DB-475A-8F9B-792EF53B331C}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>-((B1-B2)/B1)*B3*B4*B5</f>
+        <v>-7.1872499999999992E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C651359A-5A84-4809-89FE-BC8B21F6289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FABA20A-1945-4D34-A9C2-671B9B119F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,7 @@
     <sheet name="T13" sheetId="13" r:id="rId13"/>
     <sheet name="T14" sheetId="14" r:id="rId14"/>
     <sheet name="T15" sheetId="15" r:id="rId15"/>
+    <sheet name="T16" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -801,23 +802,23 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE7A069-D1DB-475A-8F9B-792EF53B331C}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>9282</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -825,7 +826,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.7</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -833,29 +834,30 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <f>-((B1-B2)/B1)*B3*B4*B5</f>
-        <v>-7.1872499999999992E-2</v>
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>(B1/B2)*B3*B4</f>
+        <v>-4.3525102348631765E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7532E11-9AE8-430C-BB7C-775C8F55C0E4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FABA20A-1945-4D34-A9C2-671B9B119F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183CA67B-9631-4E98-8A3A-55F3BD2B33E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13635" yWindow="3885" windowWidth="15915" windowHeight="10080" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="T14" sheetId="14" r:id="rId14"/>
     <sheet name="T15" sheetId="15" r:id="rId15"/>
     <sheet name="T16" sheetId="16" r:id="rId16"/>
+    <sheet name="T17" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -810,15 +811,15 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>9282</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -826,7 +827,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>-0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -834,6 +835,66 @@
         <v>4</v>
       </c>
       <c r="B4">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>((B1-B2)/B1)*B3*B4*B5</f>
+        <v>7.1872499999999992E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7532E11-9AE8-430C-BB7C-775C8F55C0E4}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>9282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
         <v>1.01</v>
       </c>
     </row>
@@ -848,16 +909,50 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239DE8D3-9E8A-4279-844C-4A45D97D6B14}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>((B1-B2)/B2) *B3</f>
+        <v>-9.3333333333333338E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7532E11-9AE8-430C-BB7C-775C8F55C0E4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183CA67B-9631-4E98-8A3A-55F3BD2B33E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F844E91-7C00-4A87-95B3-7BE0462C16E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13635" yWindow="3885" windowWidth="15915" windowHeight="10080" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13635" yWindow="3885" windowWidth="15915" windowHeight="10080" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="T15" sheetId="15" r:id="rId15"/>
     <sheet name="T16" sheetId="16" r:id="rId16"/>
     <sheet name="T17" sheetId="17" r:id="rId17"/>
+    <sheet name="T18" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -956,6 +957,50 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887B2C3D-3D13-498E-A309-97566F9E182C}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>(((B2/B1)-1)*B3)</f>
+        <v>-2.5000000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F844E91-7C00-4A87-95B3-7BE0462C16E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0425FA1C-C936-40A6-8BB0-D9A058C6E0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13635" yWindow="3885" windowWidth="15915" windowHeight="10080" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="9" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="T16" sheetId="16" r:id="rId16"/>
     <sheet name="T17" sheetId="17" r:id="rId17"/>
     <sheet name="T18" sheetId="18" r:id="rId18"/>
+    <sheet name="T21a" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1001,6 +1002,57 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788757BC-5CD0-428B-BD1C-3A13CCA94843}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <f>(B1*(B4-B3))/B2</f>
+        <v>-0.10950000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0425FA1C-C936-40A6-8BB0-D9A058C6E0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFC2594-BFB6-4D38-B61E-2D7F56054AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="9" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="T17" sheetId="17" r:id="rId17"/>
     <sheet name="T18" sheetId="18" r:id="rId18"/>
     <sheet name="T21a" sheetId="19" r:id="rId19"/>
+    <sheet name="T21b" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1096,6 +1097,101 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>307.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.32700000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <f>-1*(B1*((B4*B6*B7*B8*B9)-(B3*B5)))/(B2*B5)</f>
+        <v>5.4799999999999996E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFC2594-BFB6-4D38-B61E-2D7F56054AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3704587-7B97-43A9-9A41-0D967974D43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1021,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1046,11 +1046,12 @@
       </c>
       <c r="B5">
         <f>(B1*(B4-B3))/B2</f>
-        <v>-0.10950000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+        <v>-1.0950000000000002E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1118,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1183,7 +1184,7 @@
       </c>
       <c r="B10">
         <f>-1*(B1*((B4*B6*B7*B8*B9)-(B3*B5)))/(B2*B5)</f>
-        <v>5.4799999999999996E-3</v>
+        <v>5.4799999999999998E-4</v>
       </c>
     </row>
   </sheetData>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3704587-7B97-43A9-9A41-0D967974D43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D14536-D97F-45FF-A63C-FC0E53237C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="T18" sheetId="18" r:id="rId18"/>
     <sheet name="T21a" sheetId="19" r:id="rId19"/>
     <sheet name="T21b" sheetId="20" r:id="rId20"/>
+    <sheet name="T22cB" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1193,6 +1194,82 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.38500000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9.7200000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>-1*((B2-B1)*B3*B4*B5)/B6*B7</f>
+        <v>3.1143420000000005E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D14536-D97F-45FF-A63C-FC0E53237C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC99FC4-5B70-4298-AEA2-01F7875BB991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,8 +1260,8 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <f>-1*((B2-B1)*B3*B4*B5)/B6*B7</f>
-        <v>3.1143420000000005E-2</v>
+        <f>((B2-B1)*B3*B4*B5)/(B6*B7)</f>
+        <v>-3.2963534522176496E-4</v>
       </c>
     </row>
   </sheetData>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\GitHub\tdm-ghg-calculator\Reference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC99FC4-5B70-4298-AEA2-01F7875BB991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C61284-F47C-48DF-8CE3-3B6B8C6755E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="T21a" sheetId="19" r:id="rId19"/>
     <sheet name="T21b" sheetId="20" r:id="rId20"/>
     <sheet name="T22cB" sheetId="21" r:id="rId21"/>
+    <sheet name="T23" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -127,9 +128,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,9 +413,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -421,7 +423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -429,7 +431,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -437,7 +439,7 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -454,9 +456,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B16458-C940-4002-A635-0E8C338DCCC2}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,7 +466,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -472,7 +474,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -480,7 +482,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -488,7 +490,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -496,7 +498,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -504,7 +506,7 @@
         <v>-0.43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -512,7 +514,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -520,7 +522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -538,9 +540,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8198844C-4C52-40D3-A5CC-C3F133397CB1}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -548,7 +550,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -556,7 +558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -564,7 +566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -572,7 +574,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -580,7 +582,7 @@
         <v>307.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -588,7 +590,7 @@
         <v>763.4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -606,9 +608,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD0EB77-86F6-45D0-A287-CA923C8E64E0}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -624,7 +626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -632,7 +634,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -640,7 +642,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -648,7 +650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -665,9 +667,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB85472-F537-4DE8-92F9-12CB7CBA9F10}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +677,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -683,7 +685,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -700,9 +702,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A9B71FA-36E9-4AA9-A810-0D608806979B}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -710,7 +712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -718,15 +720,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -734,7 +736,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -742,7 +744,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -750,7 +752,7 @@
         <v>205.1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -758,7 +760,7 @@
         <v>0.32700000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -766,7 +768,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -774,7 +776,7 @@
         <v>307.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -782,7 +784,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -790,7 +792,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -808,9 +810,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE7A069-D1DB-475A-8F9B-792EF53B331C}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -818,7 +820,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -826,7 +828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -834,7 +836,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -842,7 +844,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -850,7 +852,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -868,9 +870,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7532E11-9AE8-430C-BB7C-775C8F55C0E4}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -878,7 +880,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -886,7 +888,7 @@
         <v>9282</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -894,7 +896,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -902,7 +904,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -919,9 +921,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239DE8D3-9E8A-4279-844C-4A45D97D6B14}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -929,7 +931,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -937,7 +939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -945,7 +947,7 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -963,9 +965,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887B2C3D-3D13-498E-A309-97566F9E182C}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -973,7 +975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -981,7 +983,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -989,7 +991,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1007,9 +1009,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788757BC-5CD0-428B-BD1C-3A13CCA94843}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1017,7 +1019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1025,7 +1027,7 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1033,7 +1035,7 @@
         <v>68.2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1041,7 +1043,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1059,9 +1061,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1071,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1077,7 +1079,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1085,7 +1087,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1102,12 +1104,12 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1115,7 +1117,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1123,7 +1125,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1133,7 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1139,7 +1141,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1147,7 +1149,7 @@
         <v>307.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1155,7 +1157,7 @@
         <v>0.32700000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1163,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1171,7 +1173,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1179,7 +1181,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1197,9 +1199,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1207,15 +1209,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1223,7 +1225,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1231,7 +1233,7 @@
         <v>0.38500000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1239,7 +1241,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1247,7 +1249,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1255,7 +1257,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1270,12 +1272,71 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D036EF-8CF1-4C13-9B46-8108C0132C37}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>(B2/B1) *B3*-B4*B5</f>
+        <v>-5.7000000000000002E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1283,7 +1344,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1291,7 +1352,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1299,7 +1360,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1316,9 +1377,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1326,7 +1387,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1334,7 +1395,7 @@
         <v>-0.28599999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1351,9 +1412,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5ED6D57-DE29-4DAC-A3AA-80DD11128A92}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1361,7 +1422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1369,7 +1430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1377,7 +1438,7 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1394,9 +1455,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEBE0D8-DEE9-4520-B548-EAFE23AFA71B}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1465,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1412,7 +1473,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1430,9 +1491,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D512145F-AAB1-4862-93C2-E8C630C31BD4}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1440,7 +1501,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1448,15 +1509,15 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1474,9 +1535,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE34028-78B5-4730-BB77-EDE25BEED080}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1484,7 +1545,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1492,15 +1553,15 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1518,9 +1579,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6836B869-383D-4226-9FF3-A319F5FB364A}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1590,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1537,7 +1598,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C61284-F47C-48DF-8CE3-3B6B8C6755E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD5C73F-050F-4CBA-9396-20B09991B000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8960" yWindow="4730" windowWidth="19200" windowHeight="9970" firstSheet="16" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="T21b" sheetId="20" r:id="rId20"/>
     <sheet name="T22cB" sheetId="21" r:id="rId21"/>
     <sheet name="T23" sheetId="22" r:id="rId22"/>
+    <sheet name="T24B" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1331,6 +1332,82 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105B05B6-310E-40FF-A289-A462CFD2CD1A}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>B1/B2 *(B3-B4)/B4*B5*B6*B7</f>
+        <v>-1.0000000000000002E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD5C73F-050F-4CBA-9396-20B09991B000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F77965-C934-43DA-B684-F16CD0286540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8960" yWindow="4730" windowWidth="19200" windowHeight="9970" firstSheet="16" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="16" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="T22cB" sheetId="21" r:id="rId21"/>
     <sheet name="T23" sheetId="22" r:id="rId22"/>
     <sheet name="T24B" sheetId="23" r:id="rId23"/>
+    <sheet name="T25B" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1408,6 +1409,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5EE5C2E-1F2E-408A-BC54-0F14E725BF63}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.57799999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>-1*((B2-B1)/B1)*B3*B4*B5*B6</f>
+        <v>-4.0459999999999996E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F77965-C934-43DA-B684-F16CD0286540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1908C49-234D-468B-B4B5-4365C9FF7616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="16" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="16" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="T23" sheetId="22" r:id="rId22"/>
     <sheet name="T24B" sheetId="23" r:id="rId23"/>
     <sheet name="T25B" sheetId="24" r:id="rId24"/>
+    <sheet name="T26" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1476,6 +1477,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EF6D2-2159-4E97-8BF0-19BB3D566A71}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.57799999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>-B2*((B1*B3*B4*B6)/B5)</f>
+        <v>-5.4400000000000004E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1908C49-234D-468B-B4B5-4365C9FF7616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8207685-5BF9-4167-9BBC-54AD1D416719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="16" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="6840" windowWidth="19200" windowHeight="9970" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -23,21 +23,22 @@
     <sheet name="T7" sheetId="8" r:id="rId8"/>
     <sheet name="T8" sheetId="9" r:id="rId9"/>
     <sheet name="T9" sheetId="10" r:id="rId10"/>
-    <sheet name="T11" sheetId="11" r:id="rId11"/>
-    <sheet name="T12" sheetId="12" r:id="rId12"/>
-    <sheet name="T13" sheetId="13" r:id="rId13"/>
-    <sheet name="T14" sheetId="14" r:id="rId14"/>
-    <sheet name="T15" sheetId="15" r:id="rId15"/>
-    <sheet name="T16" sheetId="16" r:id="rId16"/>
-    <sheet name="T17" sheetId="17" r:id="rId17"/>
-    <sheet name="T18" sheetId="18" r:id="rId18"/>
-    <sheet name="T21a" sheetId="19" r:id="rId19"/>
-    <sheet name="T21b" sheetId="20" r:id="rId20"/>
-    <sheet name="T22cB" sheetId="21" r:id="rId21"/>
-    <sheet name="T23" sheetId="22" r:id="rId22"/>
-    <sheet name="T24B" sheetId="23" r:id="rId23"/>
-    <sheet name="T25B" sheetId="24" r:id="rId24"/>
-    <sheet name="T26" sheetId="25" r:id="rId25"/>
+    <sheet name="T10" sheetId="26" r:id="rId11"/>
+    <sheet name="T11" sheetId="11" r:id="rId12"/>
+    <sheet name="T12" sheetId="12" r:id="rId13"/>
+    <sheet name="T13" sheetId="13" r:id="rId14"/>
+    <sheet name="T14" sheetId="14" r:id="rId15"/>
+    <sheet name="T15" sheetId="15" r:id="rId16"/>
+    <sheet name="T16" sheetId="16" r:id="rId17"/>
+    <sheet name="T17" sheetId="17" r:id="rId18"/>
+    <sheet name="T18" sheetId="18" r:id="rId19"/>
+    <sheet name="T21a" sheetId="19" r:id="rId20"/>
+    <sheet name="T21b" sheetId="20" r:id="rId21"/>
+    <sheet name="T22cB" sheetId="21" r:id="rId22"/>
+    <sheet name="T23" sheetId="22" r:id="rId23"/>
+    <sheet name="T24B" sheetId="23" r:id="rId24"/>
+    <sheet name="T25B" sheetId="24" r:id="rId25"/>
+    <sheet name="T26" sheetId="25" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -102,13 +103,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,10 +138,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,6 +551,74 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257D3EDC-3FD9-40BB-AAC7-3D328C31382A}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.85</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>(B2*(B4-(B1*B4)))/(B3*B5)</f>
+        <v>-1.9894677871148462E-2</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G8" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8198844C-4C52-40D3-A5CC-C3F133397CB1}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -608,7 +686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD0EB77-86F6-45D0-A287-CA923C8E64E0}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -667,7 +745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB85472-F537-4DE8-92F9-12CB7CBA9F10}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -702,7 +780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A9B71FA-36E9-4AA9-A810-0D608806979B}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -810,7 +888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE7A069-D1DB-475A-8F9B-792EF53B331C}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -870,7 +948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7532E11-9AE8-430C-BB7C-775C8F55C0E4}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -921,7 +999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239DE8D3-9E8A-4279-844C-4A45D97D6B14}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -965,7 +1043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887B2C3D-3D13-498E-A309-97566F9E182C}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1009,7 +1087,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B3*(B1-B2)/B2</f>
+        <v>-0.17137931034482759</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788757BC-5CD0-428B-BD1C-3A13CCA94843}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1061,50 +1182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31D2A21-89B6-449E-AB74-EE9FEB6BE116}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <f>B3*(B1-B2)/B2</f>
-        <v>-0.17137931034482759</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1199,7 +1277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1275,7 +1353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D036EF-8CF1-4C13-9B46-8108C0132C37}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1334,7 +1412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105B05B6-310E-40FF-A289-A462CFD2CD1A}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1410,7 +1488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5EE5C2E-1F2E-408A-BC54-0F14E725BF63}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1477,7 +1555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EF6D2-2159-4E97-8BF0-19BB3D566A71}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8207685-5BF9-4167-9BBC-54AD1D416719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FFF543-745A-4143-88A7-123692D63CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="6840" windowWidth="19200" windowHeight="9970" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="T24B" sheetId="23" r:id="rId24"/>
     <sheet name="T25B" sheetId="24" r:id="rId25"/>
     <sheet name="T26" sheetId="25" r:id="rId26"/>
+    <sheet name="T27" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1622,6 +1623,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E4C011-9C8B-4490-8B6D-F742F24FB084}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.57799999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>-1*(B1*B2*B3*B4*B6)/B5</f>
+        <v>-1.3004999999999998E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FFF543-745A-4143-88A7-123692D63CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873109EB-0E94-434B-A3D4-9116AD740ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -32,14 +32,15 @@
     <sheet name="T16" sheetId="16" r:id="rId17"/>
     <sheet name="T17" sheetId="17" r:id="rId18"/>
     <sheet name="T18" sheetId="18" r:id="rId19"/>
-    <sheet name="T21a" sheetId="19" r:id="rId20"/>
-    <sheet name="T21b" sheetId="20" r:id="rId21"/>
-    <sheet name="T22cB" sheetId="21" r:id="rId22"/>
-    <sheet name="T23" sheetId="22" r:id="rId23"/>
-    <sheet name="T24B" sheetId="23" r:id="rId24"/>
-    <sheet name="T25B" sheetId="24" r:id="rId25"/>
-    <sheet name="T26" sheetId="25" r:id="rId26"/>
-    <sheet name="T27" sheetId="27" r:id="rId27"/>
+    <sheet name="T20" sheetId="28" r:id="rId20"/>
+    <sheet name="T21a" sheetId="19" r:id="rId21"/>
+    <sheet name="T21b" sheetId="20" r:id="rId22"/>
+    <sheet name="T22cB" sheetId="21" r:id="rId23"/>
+    <sheet name="T23" sheetId="22" r:id="rId24"/>
+    <sheet name="T24B" sheetId="23" r:id="rId25"/>
+    <sheet name="T25B" sheetId="24" r:id="rId26"/>
+    <sheet name="T26" sheetId="25" r:id="rId27"/>
+    <sheet name="T27" sheetId="27" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1132,6 +1133,81 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6860669-536E-478F-9C8D-4895DCFE63A0}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>-1*(((B2-B1)/B1)*B3*B5*B7)/(B4*B6)</f>
+        <v>-7.7310924369747899E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788757BC-5CD0-428B-BD1C-3A13CCA94843}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1183,7 +1259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1278,7 +1354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1354,7 +1430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D036EF-8CF1-4C13-9B46-8108C0132C37}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1413,7 +1489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105B05B6-310E-40FF-A289-A462CFD2CD1A}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1489,7 +1565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5EE5C2E-1F2E-408A-BC54-0F14E725BF63}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1556,7 +1632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EF6D2-2159-4E97-8BF0-19BB3D566A71}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1623,7 +1699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E4C011-9C8B-4490-8B6D-F742F24FB084}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873109EB-0E94-434B-A3D4-9116AD740ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1813BF93-D1F8-4E46-AEF9-A7BE0F4CAE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,14 @@
     <sheet name="T18" sheetId="18" r:id="rId19"/>
     <sheet name="T20" sheetId="28" r:id="rId20"/>
     <sheet name="T21a" sheetId="19" r:id="rId21"/>
-    <sheet name="T21b" sheetId="20" r:id="rId22"/>
-    <sheet name="T22cB" sheetId="21" r:id="rId23"/>
-    <sheet name="T23" sheetId="22" r:id="rId24"/>
-    <sheet name="T24B" sheetId="23" r:id="rId25"/>
-    <sheet name="T25B" sheetId="24" r:id="rId26"/>
-    <sheet name="T26" sheetId="25" r:id="rId27"/>
-    <sheet name="T27" sheetId="27" r:id="rId28"/>
+    <sheet name="T22a" sheetId="29" r:id="rId22"/>
+    <sheet name="T21b" sheetId="20" r:id="rId23"/>
+    <sheet name="T22cB" sheetId="21" r:id="rId24"/>
+    <sheet name="T23" sheetId="22" r:id="rId25"/>
+    <sheet name="T24B" sheetId="23" r:id="rId26"/>
+    <sheet name="T25B" sheetId="24" r:id="rId27"/>
+    <sheet name="T26" sheetId="25" r:id="rId28"/>
+    <sheet name="T27" sheetId="27" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1260,6 +1261,82 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADB945E-76DD-4F0B-9374-A0D4D5770EE9}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.19600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9.7200000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>(((B2-B1)*B3*B4*B5)/(B6*B7))*-1</f>
+        <v>-1.7565614997713764E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1344,8 +1421,8 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <f>-1*(B1*((B4*B6*B7*B8*B9)-(B3*B5)))/(B2*B5)</f>
-        <v>5.4799999999999998E-4</v>
+        <f>(B1*((B4*B6*B7*B8*B9)-(B3*B5)))/(B2*B5)</f>
+        <v>-5.4799999999999998E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1430,7 +1507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D036EF-8CF1-4C13-9B46-8108C0132C37}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1489,7 +1566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105B05B6-310E-40FF-A289-A462CFD2CD1A}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1565,7 +1642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5EE5C2E-1F2E-408A-BC54-0F14E725BF63}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1632,7 +1709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EF6D2-2159-4E97-8BF0-19BB3D566A71}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1699,7 +1776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E4C011-9C8B-4490-8B6D-F742F24FB084}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1813BF93-D1F8-4E46-AEF9-A7BE0F4CAE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70B8738-5839-4B1A-AB24-6DE943C2D0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -35,13 +35,16 @@
     <sheet name="T20" sheetId="28" r:id="rId20"/>
     <sheet name="T21a" sheetId="19" r:id="rId21"/>
     <sheet name="T22a" sheetId="29" r:id="rId22"/>
-    <sheet name="T21b" sheetId="20" r:id="rId23"/>
-    <sheet name="T22cB" sheetId="21" r:id="rId24"/>
-    <sheet name="T23" sheetId="22" r:id="rId25"/>
-    <sheet name="T24B" sheetId="23" r:id="rId26"/>
-    <sheet name="T25B" sheetId="24" r:id="rId27"/>
-    <sheet name="T26" sheetId="25" r:id="rId28"/>
-    <sheet name="T27" sheetId="27" r:id="rId29"/>
+    <sheet name="T22b" sheetId="30" r:id="rId23"/>
+    <sheet name="T22c" sheetId="32" r:id="rId24"/>
+    <sheet name="T22d" sheetId="31" r:id="rId25"/>
+    <sheet name="T21b" sheetId="20" r:id="rId26"/>
+    <sheet name="T22cB" sheetId="21" r:id="rId27"/>
+    <sheet name="T23" sheetId="22" r:id="rId28"/>
+    <sheet name="T24B" sheetId="23" r:id="rId29"/>
+    <sheet name="T25B" sheetId="24" r:id="rId30"/>
+    <sheet name="T26" sheetId="25" r:id="rId31"/>
+    <sheet name="T27" sheetId="27" r:id="rId32"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -106,6 +109,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -141,13 +147,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1337,6 +1344,249 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB0BC64-71B3-4F79-95ED-EE6427AF4050}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9.7200000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>(((B2-B1)*B3*B4*B5)/(B6*B7))*-1</f>
+        <v>-3.3327617741197988E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953B5401-36F7-4AFE-839C-026FA056AD0B}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.38500000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>9.7200000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>(((B2-B1)*B3*B4*B5)/(B6*B7))*-1</f>
+        <v>-5.6038008687700046E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{027E8AEE-0803-4B02-9E46-BDF34BF75B33}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.19600000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="4">
+        <f>(((-B1*B2*B3*((B4*B5)-(B6*B7)))/(B8*B9)))</f>
+        <v>-4.2379948453608247E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1431,7 +1681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1507,7 +1757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D036EF-8CF1-4C13-9B46-8108C0132C37}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1566,7 +1816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105B05B6-310E-40FF-A289-A462CFD2CD1A}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1642,7 +1892,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>-(B2*B1)/B3</f>
+        <v>-0.21777777777777779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5EE5C2E-1F2E-408A-BC54-0F14E725BF63}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1709,7 +2002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EF6D2-2159-4E97-8BF0-19BB3D566A71}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1776,7 +2069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E4C011-9C8B-4490-8B6D-F742F24FB084}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1843,49 +2136,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <f>-(B2*B1)/B3</f>
-        <v>-0.21777777777777779</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
   <dimension ref="A1:B3"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70B8738-5839-4B1A-AB24-6DE943C2D0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D89637-0070-4658-A0F4-803531A458F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="23" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,7 @@
     <sheet name="T25B" sheetId="24" r:id="rId30"/>
     <sheet name="T26" sheetId="25" r:id="rId31"/>
     <sheet name="T27" sheetId="27" r:id="rId32"/>
+    <sheet name="T28" sheetId="33" r:id="rId33"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -110,7 +111,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -154,7 +155,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2136,6 +2137,98 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03489F6D-C13B-4D2F-B889-50C72227FDF1}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.57799999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <f>-B2*(B3*B5*((B1*B8)+(B7*B9)+B6))/B4</f>
+        <v>-0.11531099999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
   <dimension ref="A1:B3"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D89637-0070-4658-A0F4-803531A458F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC9283-0E6C-4BCE-8C3E-6938DB103540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="23" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="28" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <sheet name="T26" sheetId="25" r:id="rId31"/>
     <sheet name="T27" sheetId="27" r:id="rId32"/>
     <sheet name="T28" sheetId="33" r:id="rId33"/>
+    <sheet name="T29B" sheetId="34" r:id="rId34"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1386,7 +1387,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1411,7 +1412,7 @@
       </c>
       <c r="B8">
         <f>(((B2-B1)*B3*B4*B5)/(B6*B7))*-1</f>
-        <v>-3.3327617741197988E-4</v>
+        <v>-4.9991426611796985E-4</v>
       </c>
     </row>
   </sheetData>
@@ -2229,6 +2230,74 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D4371F-7752-4380-AAD2-3CD65C64C4E4}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.57799999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>(B1*B2*B3*B4*B6)/B5</f>
+        <v>-1.0403999999999998E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
   <dimension ref="A1:B3"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC9283-0E6C-4BCE-8C3E-6938DB103540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C99B3DB-3519-42D1-B6CA-2FD5E6829C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="28" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="28" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -47,6 +47,7 @@
     <sheet name="T27" sheetId="27" r:id="rId32"/>
     <sheet name="T28" sheetId="33" r:id="rId33"/>
     <sheet name="T29B" sheetId="34" r:id="rId34"/>
+    <sheet name="T46" sheetId="35" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -2298,6 +2299,98 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BA039-FAE9-4F58-A255-BAD81FF0BAAA}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.83299999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0.249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <f>B1*(B2/B3)*B4*(B5/B6)*(B7-B8)*B9</f>
+        <v>-7.1350758620689623E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
   <dimension ref="A1:B3"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C99B3DB-3519-42D1-B6CA-2FD5E6829C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0D2785-4AD4-4B40-ADC3-8972F8C463F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="28" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="31" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,9 @@
     <sheet name="T27" sheetId="27" r:id="rId32"/>
     <sheet name="T28" sheetId="33" r:id="rId33"/>
     <sheet name="T29B" sheetId="34" r:id="rId34"/>
-    <sheet name="T46" sheetId="35" r:id="rId35"/>
+    <sheet name="T40" sheetId="36" r:id="rId35"/>
+    <sheet name="T46" sheetId="35" r:id="rId36"/>
+    <sheet name="T56" sheetId="37" r:id="rId37"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -2300,32 +2302,32 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BA039-FAE9-4F58-A255-BAD81FF0BAAA}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>12000</v>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9A9924-ECD5-42C9-AEB6-442F006B5576}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.79</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2333,7 +2335,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.15</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2341,7 +2343,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.83299999999999996</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2349,7 +2351,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1.45</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -2357,7 +2359,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.249</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -2365,6 +2367,90 @@
         <v>8</v>
       </c>
       <c r="B8">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <f>(B1*B2*B3*((B7/B4)-((B6*B8)/B5)))/(B7/B4)</f>
+        <v>-0.13844472023010548</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BA039-FAE9-4F58-A255-BAD81FF0BAAA}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.83299999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0.249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
         <v>0.20300000000000001</v>
       </c>
     </row>
@@ -2391,6 +2477,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83802985-441C-4BBF-B305-3743B0992738}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>B2*B5*((B1-B3)/((B6*B4*(1-B2))+(B2*B3*B5)))</f>
+        <v>-2.6530420122039929E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
   <dimension ref="A1:B3"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0D2785-4AD4-4B40-ADC3-8972F8C463F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA30406-65FF-4BF6-B16F-1D2A345597A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="31" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="5010" windowWidth="19200" windowHeight="8670" firstSheet="31" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -2451,7 +2451,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.20300000000000001</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B10">
         <f>B1*(B2/B3)*B4*(B5/B6)*(B7-B8)*B9</f>
-        <v>-7.1350758620689623E-4</v>
+        <v>-1.4115041379310343E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0D2785-4AD4-4B40-ADC3-8972F8C463F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132FAC5F-8207-471D-A79A-265DEA8CD974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="31" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -32,24 +32,27 @@
     <sheet name="T16" sheetId="16" r:id="rId17"/>
     <sheet name="T17" sheetId="17" r:id="rId18"/>
     <sheet name="T18" sheetId="18" r:id="rId19"/>
-    <sheet name="T20" sheetId="28" r:id="rId20"/>
-    <sheet name="T21a" sheetId="19" r:id="rId21"/>
-    <sheet name="T22a" sheetId="29" r:id="rId22"/>
-    <sheet name="T22b" sheetId="30" r:id="rId23"/>
-    <sheet name="T22c" sheetId="32" r:id="rId24"/>
-    <sheet name="T22d" sheetId="31" r:id="rId25"/>
-    <sheet name="T21b" sheetId="20" r:id="rId26"/>
-    <sheet name="T22cB" sheetId="21" r:id="rId27"/>
-    <sheet name="T23" sheetId="22" r:id="rId28"/>
-    <sheet name="T24B" sheetId="23" r:id="rId29"/>
-    <sheet name="T25B" sheetId="24" r:id="rId30"/>
-    <sheet name="T26" sheetId="25" r:id="rId31"/>
-    <sheet name="T27" sheetId="27" r:id="rId32"/>
-    <sheet name="T28" sheetId="33" r:id="rId33"/>
-    <sheet name="T29B" sheetId="34" r:id="rId34"/>
-    <sheet name="T40" sheetId="36" r:id="rId35"/>
-    <sheet name="T46" sheetId="35" r:id="rId36"/>
-    <sheet name="T56" sheetId="37" r:id="rId37"/>
+    <sheet name="T19A" sheetId="39" r:id="rId20"/>
+    <sheet name="T19B" sheetId="40" r:id="rId21"/>
+    <sheet name="T20" sheetId="28" r:id="rId22"/>
+    <sheet name="T21a" sheetId="19" r:id="rId23"/>
+    <sheet name="T22a" sheetId="29" r:id="rId24"/>
+    <sheet name="T22b" sheetId="30" r:id="rId25"/>
+    <sheet name="T22c" sheetId="32" r:id="rId26"/>
+    <sheet name="T22d" sheetId="31" r:id="rId27"/>
+    <sheet name="T21b" sheetId="20" r:id="rId28"/>
+    <sheet name="T22cB" sheetId="21" r:id="rId29"/>
+    <sheet name="T23" sheetId="22" r:id="rId30"/>
+    <sheet name="T24B" sheetId="23" r:id="rId31"/>
+    <sheet name="T25B" sheetId="24" r:id="rId32"/>
+    <sheet name="T26" sheetId="25" r:id="rId33"/>
+    <sheet name="T27" sheetId="27" r:id="rId34"/>
+    <sheet name="T28" sheetId="33" r:id="rId35"/>
+    <sheet name="T29B" sheetId="34" r:id="rId36"/>
+    <sheet name="T30" sheetId="38" r:id="rId37"/>
+    <sheet name="T40" sheetId="36" r:id="rId38"/>
+    <sheet name="T46" sheetId="35" r:id="rId39"/>
+    <sheet name="T56" sheetId="37" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1146,6 +1149,24 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D43674-F8CA-4892-9418-1EB2C684B669}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE75B56-B57D-40E3-B6D5-EF484BAA8BB4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6860669-536E-478F-9C8D-4895DCFE63A0}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1220,7 +1241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788757BC-5CD0-428B-BD1C-3A13CCA94843}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1272,7 +1293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADB945E-76DD-4F0B-9374-A0D4D5770EE9}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1348,7 +1369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB0BC64-71B3-4F79-95ED-EE6427AF4050}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1424,7 +1445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953B5401-36F7-4AFE-839C-026FA056AD0B}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1499,7 +1520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{027E8AEE-0803-4B02-9E46-BDF34BF75B33}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1591,7 +1612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1686,7 +1707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1762,7 +1783,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>-(B2*B1)/B3</f>
+        <v>-0.21777777777777779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D036EF-8CF1-4C13-9B46-8108C0132C37}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1821,7 +1885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105B05B6-310E-40FF-A289-A462CFD2CD1A}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1897,50 +1961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <f>-(B2*B1)/B3</f>
-        <v>-0.21777777777777779</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5EE5C2E-1F2E-408A-BC54-0F14E725BF63}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2007,7 +2028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EF6D2-2159-4E97-8BF0-19BB3D566A71}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2074,7 +2095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E4C011-9C8B-4490-8B6D-F742F24FB084}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2141,7 +2162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03489F6D-C13B-4D2F-B889-50C72227FDF1}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2233,7 +2254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D4371F-7752-4380-AAD2-3CD65C64C4E4}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2301,7 +2322,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD0B3FF-71A9-44B4-A1C6-45B681ED2EB7}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B1*((B2-B3)/B3)</f>
+        <v>-0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9A9924-ECD5-42C9-AEB6-442F006B5576}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2385,7 +2449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BA039-FAE9-4F58-A255-BAD81FF0BAAA}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2477,7 +2541,42 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>B2*B1</f>
+        <v>-5.7200000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83802985-441C-4BBF-B305-3743B0992738}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2544,41 +2643,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>-0.28599999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <f>B2*B1</f>
-        <v>-5.7200000000000001E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5ED6D57-DE29-4DAC-A3AA-80DD11128A92}">
   <dimension ref="A1:B4"/>

--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132FAC5F-8207-471D-A79A-265DEA8CD974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CACA21-E4C1-44B9-AC6D-1D222A9D4844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1150,18 +1150,150 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D43674-F8CA-4892-9418-1EB2C684B669}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.07E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <f>-B1*(((B5/B8)*(B2+B3)*B4*B6)/B7)</f>
+        <v>-4.0837211763227344E-3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE75B56-B57D-40E3-B6D5-EF484BAA8BB4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.86599999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>-B1*((((B3*(B5-(B2*B5)))/(B4*B6))))</f>
+        <v>1.265378962838546E-3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
